--- a/trabGramos/outputs/tables/nn_experiments_summary.xlsx
+++ b/trabGramos/outputs/tables/nn_experiments_summary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1344" uniqueCount="92">
   <si>
     <t>config_name</t>
   </si>
@@ -391,238 +391,238 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" s="0" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G2" s="0">
-        <v>99.980000000000004</v>
+        <v>99.978000000000023</v>
       </c>
       <c r="H2" s="0">
-        <v>0</v>
+        <v>0.019888578520234124</v>
       </c>
       <c r="I2" s="0">
-        <v>99.900000000000006</v>
+        <v>99.960000000000008</v>
       </c>
       <c r="J2" s="0">
-        <v>0</v>
+        <v>0.0644061188719494</v>
       </c>
       <c r="K2" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F3" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G3" s="0">
-        <v>99.980000000000004</v>
+        <v>99.978000000000023</v>
       </c>
       <c r="H3" s="0">
-        <v>0</v>
+        <v>0.019888578520234124</v>
       </c>
       <c r="I3" s="0">
-        <v>99.900000000000006</v>
+        <v>99.960000000000008</v>
       </c>
       <c r="J3" s="0">
-        <v>0</v>
+        <v>0.0644061188719494</v>
       </c>
       <c r="K3" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="0" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G4" s="0">
-        <v>99.980000000000004</v>
+        <v>99.975999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>0</v>
+        <v>0.022705848487902358</v>
       </c>
       <c r="I4" s="0">
-        <v>99.900000000000006</v>
+        <v>99.960000000000008</v>
       </c>
       <c r="J4" s="0">
-        <v>0</v>
+        <v>0.0644061188719494</v>
       </c>
       <c r="K4" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F5" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G5" s="0">
-        <v>99.980000000000004</v>
+        <v>99.975999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>0</v>
+        <v>0.022705848487902358</v>
       </c>
       <c r="I5" s="0">
-        <v>99.900000000000006</v>
+        <v>99.960000000000008</v>
       </c>
       <c r="J5" s="0">
-        <v>0</v>
+        <v>0.0644061188719494</v>
       </c>
       <c r="K5" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" s="0" t="b">
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G6" s="0">
-        <v>99.980000000000004</v>
+        <v>99.986000000000018</v>
       </c>
       <c r="H6" s="0">
-        <v>0</v>
+        <v>0.013498971154208372</v>
       </c>
       <c r="I6" s="0">
-        <v>99.900000000000006</v>
+        <v>99.960000000000008</v>
       </c>
       <c r="J6" s="0">
-        <v>0</v>
+        <v>0.064406118871949386</v>
       </c>
       <c r="K6" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F7" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G7" s="0">
-        <v>99.980000000000004</v>
+        <v>99.986000000000018</v>
       </c>
       <c r="H7" s="0">
-        <v>0</v>
+        <v>0.013498971154208372</v>
       </c>
       <c r="I7" s="0">
-        <v>99.900000000000006</v>
+        <v>99.960000000000008</v>
       </c>
       <c r="J7" s="0">
-        <v>0</v>
+        <v>0.064406118871949386</v>
       </c>
       <c r="K7" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>42</v>
@@ -634,33 +634,33 @@
         <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G8" s="0">
-        <v>99.980000000000004</v>
+        <v>99.970000000000013</v>
       </c>
       <c r="H8" s="0">
-        <v>0</v>
+        <v>0.023570226039550245</v>
       </c>
       <c r="I8" s="0">
-        <v>99.900000000000006</v>
+        <v>99.950000000000003</v>
       </c>
       <c r="J8" s="0">
-        <v>0</v>
+        <v>0.052704627669469997</v>
       </c>
       <c r="K8" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>42</v>
@@ -672,112 +672,112 @@
         <v>1</v>
       </c>
       <c r="F9" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G9" s="0">
-        <v>99.980000000000004</v>
+        <v>99.970000000000013</v>
       </c>
       <c r="H9" s="0">
-        <v>0</v>
+        <v>0.023570226039550245</v>
       </c>
       <c r="I9" s="0">
-        <v>99.900000000000006</v>
+        <v>99.950000000000003</v>
       </c>
       <c r="J9" s="0">
-        <v>0</v>
+        <v>0.052704627669469997</v>
       </c>
       <c r="K9" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" s="0" t="b">
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G10" s="0">
-        <v>99.980000000000004</v>
+        <v>99.992000000000004</v>
       </c>
       <c r="H10" s="0">
-        <v>0</v>
+        <v>0.019321835661586323</v>
       </c>
       <c r="I10" s="0">
-        <v>99.900000000000006</v>
+        <v>99.946666666666673</v>
       </c>
       <c r="J10" s="0">
-        <v>0</v>
+        <v>0.12881223774390729</v>
       </c>
       <c r="K10" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F11" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G11" s="0">
-        <v>99.980000000000004</v>
+        <v>99.992000000000004</v>
       </c>
       <c r="H11" s="0">
-        <v>0</v>
+        <v>0.019321835661586323</v>
       </c>
       <c r="I11" s="0">
-        <v>99.900000000000006</v>
+        <v>99.946666666666673</v>
       </c>
       <c r="J11" s="0">
-        <v>0</v>
+        <v>0.12881223774390729</v>
       </c>
       <c r="K11" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>46</v>
@@ -786,36 +786,36 @@
         <v>0</v>
       </c>
       <c r="F12" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G12" s="0">
-        <v>99.980000000000004</v>
+        <v>99.966000000000022</v>
       </c>
       <c r="H12" s="0">
-        <v>0</v>
+        <v>0.023190036174568402</v>
       </c>
       <c r="I12" s="0">
-        <v>99.900000000000006</v>
+        <v>99.939999999999998</v>
       </c>
       <c r="J12" s="0">
-        <v>0</v>
+        <v>0.069920589878009282</v>
       </c>
       <c r="K12" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>46</v>
@@ -824,33 +824,33 @@
         <v>1</v>
       </c>
       <c r="F13" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G13" s="0">
-        <v>99.980000000000004</v>
+        <v>99.966000000000022</v>
       </c>
       <c r="H13" s="0">
-        <v>0</v>
+        <v>0.023190036174568402</v>
       </c>
       <c r="I13" s="0">
-        <v>99.900000000000006</v>
+        <v>99.939999999999998</v>
       </c>
       <c r="J13" s="0">
-        <v>0</v>
+        <v>0.069920589878009282</v>
       </c>
       <c r="K13" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>42</v>
@@ -862,33 +862,33 @@
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G14" s="0">
-        <v>99.960000000000008</v>
+        <v>99.969999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>0</v>
+        <v>0.02538591035288024</v>
       </c>
       <c r="I14" s="0">
-        <v>99.900000000000006</v>
+        <v>99.939999999999998</v>
       </c>
       <c r="J14" s="0">
-        <v>0</v>
+        <v>0.069920589878009282</v>
       </c>
       <c r="K14" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>42</v>
@@ -900,33 +900,33 @@
         <v>1</v>
       </c>
       <c r="F15" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G15" s="0">
-        <v>99.960000000000008</v>
+        <v>99.969999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>0</v>
+        <v>0.02538591035288024</v>
       </c>
       <c r="I15" s="0">
-        <v>99.900000000000006</v>
+        <v>99.939999999999998</v>
       </c>
       <c r="J15" s="0">
-        <v>0</v>
+        <v>0.069920589878009282</v>
       </c>
       <c r="K15" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>43</v>
@@ -938,33 +938,33 @@
         <v>0</v>
       </c>
       <c r="F16" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G16" s="0">
-        <v>99.960000000000008</v>
+        <v>99.967999999999989</v>
       </c>
       <c r="H16" s="0">
-        <v>0</v>
+        <v>0.030110906108364172</v>
       </c>
       <c r="I16" s="0">
-        <v>99.900000000000006</v>
+        <v>99.939999999999998</v>
       </c>
       <c r="J16" s="0">
-        <v>0</v>
+        <v>0.05163977794942929</v>
       </c>
       <c r="K16" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>43</v>
@@ -976,33 +976,33 @@
         <v>1</v>
       </c>
       <c r="F17" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G17" s="0">
-        <v>99.960000000000008</v>
+        <v>99.967999999999989</v>
       </c>
       <c r="H17" s="0">
-        <v>0</v>
+        <v>0.030110906108364172</v>
       </c>
       <c r="I17" s="0">
-        <v>99.900000000000006</v>
+        <v>99.939999999999998</v>
       </c>
       <c r="J17" s="0">
-        <v>0</v>
+        <v>0.05163977794942929</v>
       </c>
       <c r="K17" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>44</v>
@@ -1014,33 +1014,33 @@
         <v>0</v>
       </c>
       <c r="F18" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G18" s="0">
-        <v>99.980000000000004</v>
+        <v>99.990000000000009</v>
       </c>
       <c r="H18" s="0">
-        <v>0</v>
+        <v>0.016996731711972569</v>
       </c>
       <c r="I18" s="0">
-        <v>99.866666666666674</v>
+        <v>99.933333333333337</v>
       </c>
       <c r="J18" s="0">
-        <v>0</v>
+        <v>0.11331154474650547</v>
       </c>
       <c r="K18" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>44</v>
@@ -1052,112 +1052,112 @@
         <v>1</v>
       </c>
       <c r="F19" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G19" s="0">
-        <v>99.980000000000004</v>
+        <v>99.990000000000009</v>
       </c>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>0.016996731711972569</v>
       </c>
       <c r="I19" s="0">
-        <v>99.866666666666674</v>
+        <v>99.933333333333337</v>
       </c>
       <c r="J19" s="0">
-        <v>0</v>
+        <v>0.11331154474650547</v>
       </c>
       <c r="K19" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20" s="0" t="b">
         <v>0</v>
       </c>
       <c r="F20" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G20" s="0">
-        <v>99.980000000000004</v>
+        <v>99.986000000000018</v>
       </c>
       <c r="H20" s="0">
-        <v>0</v>
+        <v>0.018973665961010331</v>
       </c>
       <c r="I20" s="0">
-        <v>99.866666666666674</v>
+        <v>99.930000000000007</v>
       </c>
       <c r="J20" s="0">
-        <v>0</v>
+        <v>0.09486832980504982</v>
       </c>
       <c r="K20" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F21" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G21" s="0">
-        <v>99.980000000000004</v>
+        <v>99.986000000000018</v>
       </c>
       <c r="H21" s="0">
-        <v>0</v>
+        <v>0.018973665961010331</v>
       </c>
       <c r="I21" s="0">
-        <v>99.866666666666674</v>
+        <v>99.930000000000007</v>
       </c>
       <c r="J21" s="0">
-        <v>0</v>
+        <v>0.09486832980504982</v>
       </c>
       <c r="K21" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>47</v>
@@ -1166,36 +1166,36 @@
         <v>0</v>
       </c>
       <c r="F22" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G22" s="0">
-        <v>99.980000000000004</v>
+        <v>99.966000000000008</v>
       </c>
       <c r="H22" s="0">
-        <v>0</v>
+        <v>0.047187568984496948</v>
       </c>
       <c r="I22" s="0">
-        <v>99.866666666666674</v>
+        <v>99.920000000000002</v>
       </c>
       <c r="J22" s="0">
-        <v>0</v>
+        <v>0.093227453170678001</v>
       </c>
       <c r="K22" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>47</v>
@@ -1204,36 +1204,36 @@
         <v>1</v>
       </c>
       <c r="F23" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G23" s="0">
-        <v>99.980000000000004</v>
+        <v>99.966000000000008</v>
       </c>
       <c r="H23" s="0">
-        <v>0</v>
+        <v>0.047187568984496948</v>
       </c>
       <c r="I23" s="0">
-        <v>99.866666666666674</v>
+        <v>99.920000000000002</v>
       </c>
       <c r="J23" s="0">
-        <v>0</v>
+        <v>0.093227453170678001</v>
       </c>
       <c r="K23" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>47</v>
@@ -1242,36 +1242,36 @@
         <v>0</v>
       </c>
       <c r="F24" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G24" s="0">
-        <v>99.980000000000004</v>
+        <v>99.988000000000014</v>
       </c>
       <c r="H24" s="0">
-        <v>0</v>
+        <v>0.013984117975599236</v>
       </c>
       <c r="I24" s="0">
-        <v>99.866666666666674</v>
+        <v>99.920000000000002</v>
       </c>
       <c r="J24" s="0">
-        <v>0</v>
+        <v>0.093227453170678001</v>
       </c>
       <c r="K24" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>47</v>
@@ -1280,182 +1280,182 @@
         <v>1</v>
       </c>
       <c r="F25" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G25" s="0">
-        <v>99.980000000000004</v>
+        <v>99.988000000000014</v>
       </c>
       <c r="H25" s="0">
-        <v>0</v>
+        <v>0.013984117975599236</v>
       </c>
       <c r="I25" s="0">
-        <v>99.866666666666674</v>
+        <v>99.920000000000002</v>
       </c>
       <c r="J25" s="0">
-        <v>0</v>
+        <v>0.093227453170678001</v>
       </c>
       <c r="K25" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E26" s="0" t="b">
         <v>0</v>
       </c>
       <c r="F26" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G26" s="0">
-        <v>99.980000000000004</v>
+        <v>99.984000000000009</v>
       </c>
       <c r="H26" s="0">
-        <v>0</v>
+        <v>0.020655911179772141</v>
       </c>
       <c r="I26" s="0">
-        <v>99.866666666666674</v>
+        <v>99.920000000000002</v>
       </c>
       <c r="J26" s="0">
-        <v>0</v>
+        <v>0.10327955589886377</v>
       </c>
       <c r="K26" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F27" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G27" s="0">
-        <v>99.980000000000004</v>
+        <v>99.984000000000009</v>
       </c>
       <c r="H27" s="0">
-        <v>0</v>
+        <v>0.020655911179772141</v>
       </c>
       <c r="I27" s="0">
-        <v>99.866666666666674</v>
+        <v>99.920000000000002</v>
       </c>
       <c r="J27" s="0">
-        <v>0</v>
+        <v>0.10327955589886377</v>
       </c>
       <c r="K27" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E28" s="0" t="b">
         <v>0</v>
       </c>
       <c r="F28" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G28" s="0">
-        <v>99.960000000000008</v>
+        <v>99.978000000000023</v>
       </c>
       <c r="H28" s="0">
-        <v>0</v>
+        <v>0.022010098692293312</v>
       </c>
       <c r="I28" s="0">
-        <v>99.866666666666674</v>
+        <v>99.890000000000001</v>
       </c>
       <c r="J28" s="0">
-        <v>0</v>
+        <v>0.11005049346146037</v>
       </c>
       <c r="K28" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F29" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G29" s="0">
-        <v>99.960000000000008</v>
+        <v>99.978000000000023</v>
       </c>
       <c r="H29" s="0">
-        <v>0</v>
+        <v>0.022010098692293312</v>
       </c>
       <c r="I29" s="0">
-        <v>99.866666666666674</v>
+        <v>99.890000000000001</v>
       </c>
       <c r="J29" s="0">
-        <v>0</v>
+        <v>0.11005049346146037</v>
       </c>
       <c r="K29" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>40</v>
@@ -1464,36 +1464,36 @@
         <v>43</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" s="0" t="b">
         <v>0</v>
       </c>
       <c r="F30" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G30" s="0">
-        <v>99.960000000000008</v>
+        <v>99.945999999999998</v>
       </c>
       <c r="H30" s="0">
-        <v>0</v>
+        <v>0.026749870196986342</v>
       </c>
       <c r="I30" s="0">
-        <v>99.866666666666674</v>
+        <v>99.889999999999986</v>
       </c>
       <c r="J30" s="0">
-        <v>0</v>
+        <v>0.11005049346146152</v>
       </c>
       <c r="K30" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>40</v>
@@ -1502,42 +1502,42 @@
         <v>43</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E31" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F31" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G31" s="0">
-        <v>99.960000000000008</v>
+        <v>99.945999999999998</v>
       </c>
       <c r="H31" s="0">
-        <v>0</v>
+        <v>0.026749870196986342</v>
       </c>
       <c r="I31" s="0">
-        <v>99.866666666666674</v>
+        <v>99.889999999999986</v>
       </c>
       <c r="J31" s="0">
-        <v>0</v>
+        <v>0.11005049346146152</v>
       </c>
       <c r="K31" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>47</v>
@@ -1546,36 +1546,36 @@
         <v>0</v>
       </c>
       <c r="F32" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G32" s="0">
-        <v>99.960000000000008</v>
+        <v>99.962000000000018</v>
       </c>
       <c r="H32" s="0">
-        <v>0</v>
+        <v>0.028982753492377687</v>
       </c>
       <c r="I32" s="0">
-        <v>99.733333333333334</v>
+        <v>99.88000000000001</v>
       </c>
       <c r="J32" s="0">
-        <v>0</v>
+        <v>0.1167460047694544</v>
       </c>
       <c r="K32" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>47</v>
@@ -1584,36 +1584,36 @@
         <v>1</v>
       </c>
       <c r="F33" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G33" s="0">
-        <v>99.960000000000008</v>
+        <v>99.962000000000018</v>
       </c>
       <c r="H33" s="0">
-        <v>0</v>
+        <v>0.028982753492377687</v>
       </c>
       <c r="I33" s="0">
-        <v>99.733333333333334</v>
+        <v>99.88000000000001</v>
       </c>
       <c r="J33" s="0">
-        <v>0</v>
+        <v>0.1167460047694544</v>
       </c>
       <c r="K33" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>40</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>47</v>
@@ -1622,36 +1622,36 @@
         <v>0</v>
       </c>
       <c r="F34" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G34" s="0">
-        <v>99.960000000000008</v>
+        <v>99.930000000000007</v>
       </c>
       <c r="H34" s="0">
-        <v>0</v>
+        <v>0.10509255180289569</v>
       </c>
       <c r="I34" s="0">
-        <v>99.733333333333334</v>
+        <v>99.826666666666682</v>
       </c>
       <c r="J34" s="0">
-        <v>0</v>
+        <v>0.19925788241297873</v>
       </c>
       <c r="K34" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>40</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>47</v>
@@ -1660,101 +1660,101 @@
         <v>1</v>
       </c>
       <c r="F35" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G35" s="0">
-        <v>99.960000000000008</v>
+        <v>99.927999999999997</v>
       </c>
       <c r="H35" s="0">
-        <v>0</v>
+        <v>0.10464755664185826</v>
       </c>
       <c r="I35" s="0">
-        <v>99.733333333333334</v>
+        <v>99.813333333333347</v>
       </c>
       <c r="J35" s="0">
-        <v>0</v>
+        <v>0.20073937405575673</v>
       </c>
       <c r="K35" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>46</v>
       </c>
       <c r="E36" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G36" s="0">
-        <v>99.939999999999998</v>
+        <v>99.897999999999996</v>
       </c>
       <c r="H36" s="0">
-        <v>0</v>
+        <v>0.099084700018609181</v>
       </c>
       <c r="I36" s="0">
-        <v>99.700000000000003</v>
+        <v>99.809999999999988</v>
       </c>
       <c r="J36" s="0">
-        <v>0</v>
+        <v>0.17919573407620729</v>
       </c>
       <c r="K36" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>46</v>
       </c>
       <c r="E37" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G37" s="0">
-        <v>99.939999999999998</v>
+        <v>99.896000000000001</v>
       </c>
       <c r="H37" s="0">
-        <v>0</v>
+        <v>0.09697651491183068</v>
       </c>
       <c r="I37" s="0">
-        <v>99.700000000000003</v>
+        <v>99.799999999999997</v>
       </c>
       <c r="J37" s="0">
-        <v>0</v>
+        <v>0.16996731711975913</v>
       </c>
       <c r="K37" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
